--- a/data/trans_orig/P07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P07-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2007</t>
+          <t>Población según su salud general autopercibida en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32239</t>
+          <t>33607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>43326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71814</t>
+          <t>69913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>62030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96581</t>
+          <t>96269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79421</t>
+          <t>80205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>116766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131864</t>
+          <t>130745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174182</t>
+          <t>171648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219831</t>
+          <t>220155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277979</t>
+          <t>276764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204738</t>
+          <t>204090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253568</t>
+          <t>253649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246223</t>
+          <t>246908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>297142</t>
+          <t>297942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>467951</t>
+          <t>465061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>537008</t>
+          <t>537507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>252541</t>
+          <t>253302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>304781</t>
+          <t>305051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>140962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186025</t>
+          <t>183863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>408646</t>
+          <t>410920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>477897</t>
+          <t>478914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51594</t>
+          <t>51698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82378</t>
+          <t>81725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61832</t>
+          <t>62064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95635</t>
+          <t>95093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138812</t>
+          <t>137102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>41202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>70360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99902</t>
+          <t>100405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101015</t>
+          <t>103956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142606</t>
+          <t>146536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224535</t>
+          <t>224650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282579</t>
+          <t>280632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339142</t>
+          <t>339520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410053</t>
+          <t>410186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313823</t>
+          <t>319133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>376802</t>
+          <t>376544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371957</t>
+          <t>373199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>436122</t>
+          <t>438656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>705823</t>
+          <t>705612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>799703</t>
+          <t>793229</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319523</t>
+          <t>320520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382472</t>
+          <t>381546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170479</t>
+          <t>172167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221216</t>
+          <t>223625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507820</t>
+          <t>503484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>589779</t>
+          <t>589726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95166</t>
+          <t>93952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138005</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76584</t>
+          <t>78076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148819</t>
+          <t>148028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203454</t>
+          <t>202380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24042</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76573</t>
+          <t>74461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114407</t>
+          <t>110901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134856</t>
+          <t>135781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177618</t>
+          <t>178770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219050</t>
+          <t>217907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277667</t>
+          <t>275410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>250821</t>
+          <t>250594</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305749</t>
+          <t>306167</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>261598</t>
+          <t>262096</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>311829</t>
+          <t>311528</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>530107</t>
+          <t>526927</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>604617</t>
+          <t>598882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193647</t>
+          <t>193413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243230</t>
+          <t>245194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135077</t>
+          <t>138895</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179807</t>
+          <t>182103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>344984</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>411688</t>
+          <t>414852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>57978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90114</t>
+          <t>91672</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45261</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>73785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109191</t>
+          <t>112055</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>155020</t>
+          <t>155256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>75383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>60867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94414</t>
+          <t>93958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138970</t>
+          <t>140095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>187917</t>
+          <t>189603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>241424</t>
+          <t>238720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>302493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>369573</t>
+          <t>368202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>325355</t>
+          <t>323606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>382188</t>
+          <t>381846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>375998</t>
+          <t>377405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>443063</t>
+          <t>441131</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>716613</t>
+          <t>720810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>808272</t>
+          <t>804273</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>317493</t>
+          <t>320906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>374003</t>
+          <t>379504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233734</t>
+          <t>235666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288597</t>
+          <t>291273</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>565967</t>
+          <t>568625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>650647</t>
+          <t>652097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>86846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128447</t>
+          <t>125874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114807</t>
+          <t>115565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>172668</t>
+          <t>173731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>228161</t>
+          <t>229818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>100673</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169844</t>
+          <t>168540</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>222364</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>245852</t>
+          <t>244314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>309821</t>
+          <t>308535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>394920</t>
+          <t>395416</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>472126</t>
+          <t>469415</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717831</t>
+          <t>724357</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>816921</t>
+          <t>825377</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1145824</t>
+          <t>1149422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1269087</t>
+          <t>1264869</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1155659</t>
+          <t>1159061</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1262316</t>
+          <t>1271312</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1311918</t>
+          <t>1315480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1422408</t>
+          <t>1434115</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2495830</t>
+          <t>2495734</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2659690</t>
+          <t>2659599</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1138410</t>
+          <t>1140496</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1251695</t>
+          <t>1245941</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>731544</t>
+          <t>734063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>830964</t>
+          <t>826890</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1897226</t>
+          <t>1899312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2054271</t>
+          <t>2047057</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>321219</t>
+          <t>321298</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>396703</t>
+          <t>397844</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>230790</t>
+          <t>230193</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>292755</t>
+          <t>293791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>572784</t>
+          <t>571076</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>666791</t>
+          <t>667699</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2012</t>
+          <t>Población según su salud general autopercibida en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>33894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94168</t>
+          <t>92742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76566</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117386</t>
+          <t>116998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127134</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170233</t>
+          <t>169152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217823</t>
+          <t>219831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278418</t>
+          <t>277945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267183</t>
+          <t>267044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>320280</t>
+          <t>320646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277357</t>
+          <t>278478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331712</t>
+          <t>330946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>557761</t>
+          <t>559445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>633187</t>
+          <t>639245</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160893</t>
+          <t>159199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206473</t>
+          <t>205618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115225</t>
+          <t>115919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159912</t>
+          <t>159941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287087</t>
+          <t>289972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353716</t>
+          <t>352096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82955</t>
+          <t>83774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121113</t>
+          <t>121542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>49360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81349</t>
+          <t>79886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143471</t>
+          <t>139625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190639</t>
+          <t>189736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>71642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>67868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>104792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125375</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174167</t>
+          <t>174587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197325</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256221</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>336592</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412909</t>
+          <t>410984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384232</t>
+          <t>384477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>452037</t>
+          <t>447815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>421599</t>
+          <t>424622</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>485989</t>
+          <t>489411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>826869</t>
+          <t>826667</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>918482</t>
+          <t>919683</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267879</t>
+          <t>269317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>326313</t>
+          <t>327223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>194378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250081</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479638</t>
+          <t>474814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>562341</t>
+          <t>558389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103207</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>146464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92335</t>
+          <t>90296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169641</t>
+          <t>166441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224994</t>
+          <t>221491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87121</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129526</t>
+          <t>128257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146957</t>
+          <t>149456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195634</t>
+          <t>198594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247804</t>
+          <t>246435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313011</t>
+          <t>310234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>273224</t>
+          <t>274702</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>329320</t>
+          <t>327915</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281033</t>
+          <t>282666</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>339520</t>
+          <t>338581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>573468</t>
+          <t>570241</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>654315</t>
+          <t>653406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>215815</t>
+          <t>215712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>268084</t>
+          <t>269973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>179088</t>
+          <t>178549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232759</t>
+          <t>230662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>411201</t>
+          <t>413863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>483596</t>
+          <t>483992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>71468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107935</t>
+          <t>109522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>61508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112525</t>
+          <t>112266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159355</t>
+          <t>159009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>45294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66565</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102811</t>
+          <t>103210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96731</t>
+          <t>95778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138152</t>
+          <t>134937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175761</t>
+          <t>173625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227842</t>
+          <t>227790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>283431</t>
+          <t>283129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>349400</t>
+          <t>349797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>384641</t>
+          <t>386381</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>446655</t>
+          <t>449786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>467415</t>
+          <t>467048</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>531606</t>
+          <t>531419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>870964</t>
+          <t>868281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>961650</t>
+          <t>961231</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>274110</t>
+          <t>271655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>333058</t>
+          <t>331679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211733</t>
+          <t>210079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266429</t>
+          <t>265092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>500646</t>
+          <t>500230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>581633</t>
+          <t>578156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71209</t>
+          <t>70273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106873</t>
+          <t>107720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>70847</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123174</t>
+          <t>121013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>169266</t>
+          <t>168964</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>81954</t>
+          <t>83035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>123543</t>
+          <t>125106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>176180</t>
+          <t>176019</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>235676</t>
+          <t>236043</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>269550</t>
+          <t>271430</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340260</t>
+          <t>338712</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>427711</t>
+          <t>428239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>516803</t>
+          <t>514958</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>693944</t>
+          <t>695294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>795533</t>
+          <t>796776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1151982</t>
+          <t>1156691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1278705</t>
+          <t>1281603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1369870</t>
+          <t>1369019</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1490975</t>
+          <t>1485395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1507543</t>
+          <t>1504362</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1631234</t>
+          <t>1631093</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2911359</t>
+          <t>2900455</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3084706</t>
+          <t>3070826</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>971288</t>
+          <t>967346</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1076560</t>
+          <t>1079344</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>749918</t>
+          <t>749107</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>852702</t>
+          <t>851667</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1747901</t>
+          <t>1748464</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1897859</t>
+          <t>1892935</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>359755</t>
+          <t>360598</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>442318</t>
+          <t>439257</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>206972</t>
+          <t>208134</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>269086</t>
+          <t>266588</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>586919</t>
+          <t>592758</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>686053</t>
+          <t>683465</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2016</t>
+          <t>Población según su salud general autopercibida en 2016 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>30684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57542</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83419</t>
+          <t>81555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73476</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110038</t>
+          <t>108786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117940</t>
+          <t>118440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161370</t>
+          <t>160269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205194</t>
+          <t>204517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256892</t>
+          <t>257848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>195960</t>
+          <t>194193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245499</t>
+          <t>244784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181347</t>
+          <t>180622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>229305</t>
+          <t>227571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>390626</t>
+          <t>390824</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>458919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>186722</t>
+          <t>184045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233430</t>
+          <t>232768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162872</t>
+          <t>161312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210152</t>
+          <t>207072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>362264</t>
+          <t>359264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>428459</t>
+          <t>425650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115614</t>
+          <t>113609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155148</t>
+          <t>157161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>84302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119593</t>
+          <t>121696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208826</t>
+          <t>211135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>262294</t>
+          <t>265849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>92920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113242</t>
+          <t>113064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157421</t>
+          <t>157574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175727</t>
+          <t>173344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231427</t>
+          <t>228228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302342</t>
+          <t>302723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371697</t>
+          <t>370929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263012</t>
+          <t>265000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324699</t>
+          <t>323815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>284677</t>
+          <t>285939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345335</t>
+          <t>347720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>570015</t>
+          <t>567858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>652519</t>
+          <t>651619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>362957</t>
+          <t>365257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>424933</t>
+          <t>427311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311000</t>
+          <t>314161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>373073</t>
+          <t>373679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>695873</t>
+          <t>692613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>783943</t>
+          <t>783018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150647</t>
+          <t>148704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202955</t>
+          <t>196262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>112691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155704</t>
+          <t>154307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272511</t>
+          <t>271373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338188</t>
+          <t>338494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50811</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76983</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81349</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118568</t>
+          <t>117237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115233</t>
+          <t>114727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161480</t>
+          <t>159069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207632</t>
+          <t>206272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264712</t>
+          <t>263221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208691</t>
+          <t>209880</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>262722</t>
+          <t>260765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>220120</t>
+          <t>219417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>273620</t>
+          <t>273280</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>442726</t>
+          <t>441509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>516311</t>
+          <t>515976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>218690</t>
+          <t>221132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>273689</t>
+          <t>276063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>205045</t>
+          <t>202244</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>258355</t>
+          <t>255654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>440304</t>
+          <t>439334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>511264</t>
+          <t>516311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>135880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185210</t>
+          <t>183002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115616</t>
+          <t>116252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156071</t>
+          <t>160667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>266163</t>
+          <t>266819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329346</t>
+          <t>328283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47164</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81693</t>
+          <t>80610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>64026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104952</t>
+          <t>103748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99241</t>
+          <t>100012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141053</t>
+          <t>140235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>152529</t>
+          <t>152307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206204</t>
+          <t>203672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265059</t>
+          <t>268008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>329940</t>
+          <t>331550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>285323</t>
+          <t>283188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>340940</t>
+          <t>339541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>336218</t>
+          <t>337232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>397101</t>
+          <t>399412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>643121</t>
+          <t>637983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>723370</t>
+          <t>723878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>326691</t>
+          <t>328057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>388678</t>
+          <t>388077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>292789</t>
+          <t>290267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>355335</t>
+          <t>351163</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>636395</t>
+          <t>633844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>719732</t>
+          <t>719075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>104892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>146244</t>
+          <t>144592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95009</t>
+          <t>94523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136295</t>
+          <t>135225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>208109</t>
+          <t>210322</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267195</t>
+          <t>268936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73406</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112583</t>
+          <t>111320</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163011</t>
+          <t>165403</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219652</t>
+          <t>223344</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>244946</t>
+          <t>250591</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>313508</t>
+          <t>324326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>400818</t>
+          <t>404063</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>478422</t>
+          <t>477921</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>606098</t>
+          <t>606743</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>704416</t>
+          <t>703928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1037882</t>
+          <t>1034068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1163466</t>
+          <t>1152650</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>999191</t>
+          <t>1005923</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1118393</t>
+          <t>1121733</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1074428</t>
+          <t>1074943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1186993</t>
+          <t>1192481</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2114233</t>
+          <t>2114228</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2268763</t>
+          <t>2278213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1147372</t>
+          <t>1151851</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1264225</t>
+          <t>1265178</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1022748</t>
+          <t>1022812</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1130412</t>
+          <t>1135114</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2205001</t>
+          <t>2208784</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2370597</t>
+          <t>2364626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>548782</t>
+          <t>547971</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>637254</t>
+          <t>637578</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>441022</t>
+          <t>443375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>524498</t>
+          <t>523357</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1013345</t>
+          <t>1017759</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1134022</t>
+          <t>1135694</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2023</t>
+          <t>Población según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54614</t>
+          <t>54772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80487</t>
+          <t>79033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101998</t>
+          <t>100266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142188</t>
+          <t>139099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115085</t>
+          <t>114511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164624</t>
+          <t>162845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229273</t>
+          <t>230216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>292644</t>
+          <t>292266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>218256</t>
+          <t>219834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>270041</t>
+          <t>271408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>285672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>413016</t>
+          <t>405036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>521116</t>
+          <t>523583</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>670339</t>
+          <t>665346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>154940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202177</t>
+          <t>203416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130244</t>
+          <t>133696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190816</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305377</t>
+          <t>304262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382404</t>
+          <t>381282</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100292</t>
+          <t>98564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66121</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91817</t>
+          <t>90570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>152796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>40004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>61751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>98197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145172</t>
+          <t>143698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166817</t>
+          <t>166348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204988</t>
+          <t>204153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186618</t>
+          <t>195182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340859</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434876</t>
+          <t>431105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>866621</t>
+          <t>910445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>361931</t>
+          <t>360352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>413670</t>
+          <t>411551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825977</t>
+          <t>818767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1363496</t>
+          <t>1368393</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178141</t>
+          <t>154986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>426993</t>
+          <t>429235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231029</t>
+          <t>231847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280815</t>
+          <t>279727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388789</t>
+          <t>390014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>671504</t>
+          <t>678319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>63063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175084</t>
+          <t>177043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99184</t>
+          <t>100954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138220</t>
+          <t>139709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253176</t>
+          <t>251839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64773</t>
+          <t>66571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71350</t>
+          <t>70970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109521</t>
+          <t>106695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64162</t>
+          <t>54759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>163855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134323</t>
+          <t>141536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246301</t>
+          <t>248433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>265979</t>
+          <t>264690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>328700</t>
+          <t>325549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>385975</t>
+          <t>385337</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>705108</t>
+          <t>719115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>688113</t>
+          <t>679640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1111957</t>
+          <t>1089077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>181293</t>
+          <t>180763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238549</t>
+          <t>235164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93158</t>
+          <t>93362</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245070</t>
+          <t>247000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>258218</t>
+          <t>248178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>458285</t>
+          <t>458276</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66357</t>
+          <t>68316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119203</t>
+          <t>119624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>41532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184617</t>
+          <t>203381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112210</t>
+          <t>116818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261951</t>
+          <t>285377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25305</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48238</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>76458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81391</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113763</t>
+          <t>114711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118436</t>
+          <t>120246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162957</t>
+          <t>162213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148460</t>
+          <t>153235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211456</t>
+          <t>214757</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286603</t>
+          <t>288446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>361255</t>
+          <t>359654</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>405073</t>
+          <t>405622</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>468829</t>
+          <t>467931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>496021</t>
+          <t>494625</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>649192</t>
+          <t>646590</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>924162</t>
+          <t>924625</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1111967</t>
+          <t>1098842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>176654</t>
+          <t>175638</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>232363</t>
+          <t>232133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186156</t>
+          <t>180602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259635</t>
+          <t>258852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376399</t>
+          <t>378756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>475005</t>
+          <t>471150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>88155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>142670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89955</t>
+          <t>87789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152140</t>
+          <t>146550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>219772</t>
+          <t>217836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88738</t>
+          <t>88219</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>135226</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148055</t>
+          <t>146199</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205100</t>
+          <t>205951</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>257339</t>
+          <t>252208</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>329809</t>
+          <t>326297</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>361866</t>
+          <t>351484</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>511125</t>
+          <t>510852</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>524246</t>
+          <t>513793</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>697688</t>
+          <t>696266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>954221</t>
+          <t>942440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1181517</t>
+          <t>1183399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1408975</t>
+          <t>1413722</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1986044</t>
+          <t>1978862</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1618868</t>
+          <t>1615996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2158363</t>
+          <t>2147106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3093065</t>
+          <t>3091583</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3845449</t>
+          <t>3898991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>717042</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1015719</t>
+          <t>1010115</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>680293</t>
+          <t>683480</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>916194</t>
+          <t>913907</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1501642</t>
+          <t>1521395</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1882819</t>
+          <t>1888703</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>309749</t>
+          <t>307717</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>464120</t>
+          <t>457286</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>234626</t>
+          <t>231113</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>396654</t>
+          <t>394487</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>580365</t>
+          <t>581141</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>788273</t>
+          <t>795787</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
